--- a/program.xlsx
+++ b/program.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/Poster/gwdaw26/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7853FE0-0E24-DB4B-B678-9AF99619F70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,7 @@
     <sheet name="48383" sheetId="4" r:id="rId4"/>
     <sheet name="48385" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -38,12 +44,6 @@
     <t>end_date</t>
   </si>
   <si>
-    <t>GWADW2026 - Gravitational-Wave Advanced Detector Workshop</t>
-  </si>
-  <si>
-    <t>Hotel Hermitage, La Biodola, Isola d'Elba</t>
-  </si>
-  <si>
     <t>2026-05-17</t>
   </si>
   <si>
@@ -708,13 +708,19 @@
   </si>
   <si>
     <t>University of Urbino Carlo Bo</t>
+  </si>
+  <si>
+    <t>La Biodola</t>
+  </si>
+  <si>
+    <t>Gravitational-Wave Advanced Detector Workshop</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -777,13 +783,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -821,7 +835,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -855,6 +869,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -889,9 +904,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1064,15 +1080,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="100.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1080,36 +1096,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1118,55 +1134,55 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" customWidth="1"/>
-    <col min="3" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="100.6640625" customWidth="1"/>
+    <col min="3" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>48383</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>48385</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1175,19 +1191,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="20.7109375" customWidth="1"/>
+    <col min="1" max="2" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1196,538 +1212,538 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="100.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="60.7109375" customWidth="1"/>
+    <col min="1" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
+    <col min="4" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1736,517 +1752,517 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="100.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="60.7109375" customWidth="1"/>
+    <col min="1" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
+    <col min="4" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F8" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F11" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F12" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F14" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F15" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D18" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E19" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E20" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E22" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E23" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E24" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F25" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E26" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F26" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F28" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E29" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F29" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F30" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D31" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F31" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/Poster/gwdaw26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7853FE0-0E24-DB4B-B678-9AF99619F70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F97A46-6D22-454A-8ED5-D8E2E6C7509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1220" yWindow="1020" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -713,7 +713,7 @@
     <t>La Biodola</t>
   </si>
   <si>
-    <t>Gravitational-Wave Advanced Detector Workshop</t>
+    <t>GWDAW26</t>
   </si>
 </sst>
 </file>

--- a/program.xlsx
+++ b/program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/Poster/gwdaw26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F97A46-6D22-454A-8ED5-D8E2E6C7509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355BBF46-38F1-1044-AE53-012E16870C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1220" yWindow="1020" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="231">
   <si>
     <t>Key</t>
   </si>
@@ -713,7 +713,10 @@
     <t>La Biodola</t>
   </si>
   <si>
-    <t>GWDAW26</t>
+    <t>pi5pm32</t>
+  </si>
+  <si>
+    <t>GWDAW 2026</t>
   </si>
 </sst>
 </file>
@@ -779,7 +782,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1101,7 +1104,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1192,7 +1195,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="20.6640625" customWidth="1"/>
@@ -1204,6 +1207,14 @@
       </c>
       <c r="B1" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1246,6 +1257,9 @@
       <c r="A2">
         <v>13</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
@@ -1263,6 +1277,9 @@
       <c r="A3">
         <v>17</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3" t="s">
         <v>26</v>
       </c>
@@ -1280,6 +1297,9 @@
       <c r="A4">
         <v>19</v>
       </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
@@ -1297,6 +1317,9 @@
       <c r="A5">
         <v>21</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
@@ -1314,6 +1337,9 @@
       <c r="A6">
         <v>25</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
       <c r="C6" t="s">
         <v>29</v>
       </c>
@@ -1331,6 +1357,9 @@
       <c r="A7">
         <v>27</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
@@ -1348,6 +1377,9 @@
       <c r="A8">
         <v>32</v>
       </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
       <c r="C8" t="s">
         <v>31</v>
       </c>
@@ -1365,6 +1397,9 @@
       <c r="A9">
         <v>42</v>
       </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
@@ -1382,6 +1417,9 @@
       <c r="A10">
         <v>44</v>
       </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
       <c r="C10" t="s">
         <v>33</v>
       </c>
@@ -1399,6 +1437,9 @@
       <c r="A11">
         <v>48</v>
       </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
       <c r="C11" t="s">
         <v>34</v>
       </c>
@@ -1416,6 +1457,9 @@
       <c r="A12">
         <v>49</v>
       </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="C12" t="s">
         <v>35</v>
       </c>
@@ -1433,6 +1477,9 @@
       <c r="A13">
         <v>52</v>
       </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="C13" t="s">
         <v>36</v>
       </c>
@@ -1450,6 +1497,9 @@
       <c r="A14">
         <v>54</v>
       </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
       <c r="C14" t="s">
         <v>37</v>
       </c>
@@ -1467,6 +1517,9 @@
       <c r="A15">
         <v>59</v>
       </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
       <c r="C15" t="s">
         <v>38</v>
       </c>
@@ -1484,6 +1537,9 @@
       <c r="A16">
         <v>60</v>
       </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
       <c r="C16" t="s">
         <v>39</v>
       </c>
@@ -1501,6 +1557,9 @@
       <c r="A17">
         <v>64</v>
       </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
       <c r="C17" t="s">
         <v>40</v>
       </c>
@@ -1518,6 +1577,9 @@
       <c r="A18">
         <v>70</v>
       </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
@@ -1535,6 +1597,9 @@
       <c r="A19">
         <v>71</v>
       </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
@@ -1549,6 +1614,9 @@
       <c r="A20">
         <v>76</v>
       </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
       <c r="C20" t="s">
         <v>43</v>
       </c>
@@ -1566,6 +1634,9 @@
       <c r="A21">
         <v>78</v>
       </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
       <c r="C21" t="s">
         <v>44</v>
       </c>
@@ -1583,6 +1654,9 @@
       <c r="A22">
         <v>84</v>
       </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
       <c r="C22" t="s">
         <v>45</v>
       </c>
@@ -1600,6 +1674,9 @@
       <c r="A23">
         <v>92</v>
       </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
       <c r="C23" t="s">
         <v>46</v>
       </c>
@@ -1617,6 +1694,9 @@
       <c r="A24">
         <v>101</v>
       </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
       <c r="C24" t="s">
         <v>47</v>
       </c>
@@ -1631,6 +1711,9 @@
       <c r="A25">
         <v>103</v>
       </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
       <c r="C25" t="s">
         <v>48</v>
       </c>
@@ -1648,6 +1731,9 @@
       <c r="A26">
         <v>107</v>
       </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
       <c r="C26" t="s">
         <v>49</v>
       </c>
@@ -1665,6 +1751,9 @@
       <c r="A27">
         <v>114</v>
       </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
       <c r="C27" t="s">
         <v>50</v>
       </c>
@@ -1682,6 +1771,9 @@
       <c r="A28">
         <v>122</v>
       </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
       <c r="C28" t="s">
         <v>51</v>
       </c>
@@ -1699,6 +1791,9 @@
       <c r="A29">
         <v>126</v>
       </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
       <c r="C29" t="s">
         <v>52</v>
       </c>
@@ -1716,6 +1811,9 @@
       <c r="A30">
         <v>127</v>
       </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
       <c r="C30" t="s">
         <v>53</v>
       </c>
@@ -1732,6 +1830,9 @@
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>132</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
       </c>
       <c r="C31" t="s">
         <v>54</v>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/Poster/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519E494F-E047-3546-8787-35C4EA7CD960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3238D47-6737-7542-BADE-BA94953678DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -822,7 +822,7 @@
     <t>La Biodola</t>
   </si>
   <si>
-    <t>GWADW 2026 ISOLA D'ELPBA 3ifjekbfierfiein</t>
+    <t>GWADW 2026 ISOLA D'ELPBA 3ifjekbfierfieinboijferoijfoeirjfvoierjgoieroieoeri</t>
   </si>
 </sst>
 </file>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marco/work/git/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAD7441-8FDD-284A-8EBB-3F8EA43E9688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE564B29-416A-4243-9EB2-55D459B5C096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -810,9 +810,6 @@
     <t>pi5pm28</t>
   </si>
   <si>
-    <t>2025-05-19 18:00:00</t>
-  </si>
-  <si>
     <t>2026-05-20 21:00:00</t>
   </si>
   <si>
@@ -823,6 +820,9 @@
   </si>
   <si>
     <t>GWADW 2026</t>
+  </si>
+  <si>
+    <t>2025-05-15 18:00:00</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1193,7 +1193,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1534,10 +1534,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1548,10 +1548,10 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1562,10 +1562,10 @@
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1576,10 +1576,10 @@
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1590,10 +1590,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1604,10 +1604,10 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1618,10 +1618,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1632,10 +1632,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1646,10 +1646,10 @@
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/program.xlsx
+++ b/program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marco/work/git/gwadw2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/Poster/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B860AEE-E8B8-2C41-8999-FB9EA65280E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F85F941-BCAF-D542-BB4D-86D1C60DBFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -819,10 +819,10 @@
     <t>2025-05-15 18:00:00</t>
   </si>
   <si>
-    <t>2026-05-16 16:10:00</t>
-  </si>
-  <si>
-    <t>2026-05-16 16:20:00</t>
+    <t>2026-05-19 13:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-21 18:20:00</t>
   </si>
 </sst>
 </file>
@@ -863,7 +863,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/Poster/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F85F941-BCAF-D542-BB4D-86D1C60DBFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCBACDC-A06B-5943-AC5E-578B6063F49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="268">
   <si>
     <t>Key</t>
   </si>
@@ -507,9 +507,6 @@
     <t>Yokozawa</t>
   </si>
   <si>
-    <t>Desalvo</t>
-  </si>
-  <si>
     <t>Eckhardt</t>
   </si>
   <si>
@@ -823,6 +820,21 @@
   </si>
   <si>
     <t>2026-05-21 18:20:00</t>
+  </si>
+  <si>
+    <t>National Astronomical Obsevatory of Japan</t>
+  </si>
+  <si>
+    <t>Université Paris Cité</t>
+  </si>
+  <si>
+    <t>DeSalvo</t>
+  </si>
+  <si>
+    <t>California State University</t>
+  </si>
+  <si>
+    <t>University of Birmingham</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1197,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1193,7 +1205,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1256,16 +1268,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1276,16 +1288,16 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1296,16 +1308,16 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -1352,16 +1364,16 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1372,16 +1384,16 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D3" t="s">
         <v>132</v>
       </c>
       <c r="E3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1392,13 +1404,13 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F4" t="s">
         <v>108</v>
@@ -1412,16 +1424,16 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -1468,16 +1480,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E2" t="s">
         <v>227</v>
       </c>
-      <c r="E2" t="s">
-        <v>228</v>
-      </c>
       <c r="F2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1488,13 +1500,16 @@
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D3" t="s">
         <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>228</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1534,10 +1549,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1548,10 +1563,10 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1562,10 +1577,10 @@
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1576,10 +1591,10 @@
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1590,10 +1605,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1604,10 +1619,10 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1618,10 +1633,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1632,10 +1647,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1646,10 +1661,10 @@
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -1675,7 +1690,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1683,7 +1698,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1691,7 +1706,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1699,7 +1714,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1707,7 +1722,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1715,7 +1730,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1723,7 +1738,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1731,7 +1746,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1739,7 +1754,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1747,7 +1762,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1755,7 +1770,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1763,7 +1778,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -1771,7 +1786,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -1779,7 +1794,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -1787,7 +1802,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -1795,7 +1810,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -1803,7 +1818,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -1811,7 +1826,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -1819,7 +1834,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -1827,7 +1842,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -1835,7 +1850,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -1843,7 +1858,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -1851,7 +1866,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -1859,7 +1874,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -1867,7 +1882,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -1875,7 +1890,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -1883,7 +1898,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -1891,7 +1906,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -2345,6 +2360,9 @@
       <c r="E7" t="s">
         <v>100</v>
       </c>
+      <c r="F7" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -2361,6 +2379,9 @@
       </c>
       <c r="E8" t="s">
         <v>101</v>
+      </c>
+      <c r="F8" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2687,6 +2708,9 @@
       <c r="E2" t="s">
         <v>155</v>
       </c>
+      <c r="F2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -2705,7 +2729,7 @@
         <v>156</v>
       </c>
       <c r="F3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2725,7 +2749,7 @@
         <v>157</v>
       </c>
       <c r="F4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2742,7 +2766,10 @@
         <v>153</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>265</v>
+      </c>
+      <c r="F5" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2759,7 +2786,10 @@
         <v>153</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>265</v>
+      </c>
+      <c r="F6" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2776,7 +2806,10 @@
         <v>153</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>265</v>
+      </c>
+      <c r="F7" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2793,7 +2826,10 @@
         <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>265</v>
+      </c>
+      <c r="F8" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2810,7 +2846,10 @@
         <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>265</v>
+      </c>
+      <c r="F9" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2827,10 +2866,10 @@
         <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -2847,10 +2886,10 @@
         <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2897,16 +2936,16 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
         <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2917,16 +2956,16 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2937,16 +2976,16 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2957,16 +2996,16 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2977,16 +3016,16 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2997,7 +3036,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
@@ -3017,13 +3056,16 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
         <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>265</v>
+      </c>
+      <c r="F8" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -3034,16 +3076,16 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -3054,13 +3096,16 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>189</v>
+        <v>188</v>
+      </c>
+      <c r="F10" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -3071,16 +3116,16 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
         <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -3091,16 +3136,16 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8545FE49-A843-514C-BECE-ED4F7B3AFC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515D9B3F-764B-974E-B1FA-A4E674B1BFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -816,9 +816,6 @@
     <t>2025-05-15 18:00:00</t>
   </si>
   <si>
-    <t>2026-05-19 13:00:00</t>
-  </si>
-  <si>
     <t>2026-05-21 18:20:00</t>
   </si>
   <si>
@@ -835,6 +832,9 @@
   </si>
   <si>
     <t>University of Birmingham</t>
+  </si>
+  <si>
+    <t>2026-05-20 13:00:00</t>
   </si>
 </sst>
 </file>
@@ -1549,7 +1549,7 @@
         <v>260</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1563,7 +1563,7 @@
         <v>260</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1577,7 +1577,7 @@
         <v>260</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1591,7 +1591,7 @@
         <v>260</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1602,10 +1602,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1616,10 +1616,10 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1630,10 +1630,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1644,10 +1644,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1658,10 +1658,10 @@
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2355,7 +2355,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2375,7 +2375,7 @@
         <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2757,10 +2757,10 @@
         <v>153</v>
       </c>
       <c r="E5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5" t="s">
         <v>265</v>
-      </c>
-      <c r="F5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2777,10 +2777,10 @@
         <v>153</v>
       </c>
       <c r="E6" t="s">
+        <v>264</v>
+      </c>
+      <c r="F6" t="s">
         <v>265</v>
-      </c>
-      <c r="F6" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2797,10 +2797,10 @@
         <v>153</v>
       </c>
       <c r="E7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F7" t="s">
         <v>265</v>
-      </c>
-      <c r="F7" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2817,10 +2817,10 @@
         <v>153</v>
       </c>
       <c r="E8" t="s">
+        <v>264</v>
+      </c>
+      <c r="F8" t="s">
         <v>265</v>
-      </c>
-      <c r="F8" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2837,10 +2837,10 @@
         <v>153</v>
       </c>
       <c r="E9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F9" t="s">
         <v>265</v>
-      </c>
-      <c r="F9" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -3053,10 +3053,10 @@
         <v>153</v>
       </c>
       <c r="E8" t="s">
+        <v>264</v>
+      </c>
+      <c r="F8" t="s">
         <v>265</v>
-      </c>
-      <c r="F8" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -3096,7 +3096,7 @@
         <v>188</v>
       </c>
       <c r="F10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6824924-7D03-0240-B9DA-71D1F660A84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4705BC3-D779-2F43-AC21-B2D7246126E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -2403,7 +2403,7 @@
         <v>132</v>
       </c>
       <c r="B10">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
         <v>85</v>
@@ -2459,7 +2459,7 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -2479,7 +2479,7 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>110</v>
@@ -2499,7 +2499,7 @@
         <v>48</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>111</v>
@@ -2519,7 +2519,7 @@
         <v>107</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>112</v>
@@ -2539,7 +2539,7 @@
         <v>114</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>113</v>
@@ -2595,7 +2595,7 @@
         <v>49</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
         <v>128</v>
@@ -2615,7 +2615,7 @@
         <v>52</v>
       </c>
       <c r="B3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
         <v>129</v>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759F8142-4713-6B49-B330-E67547544EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB60B704-E23D-7845-8114-55B8147CCCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="264">
   <si>
     <t>Key</t>
   </si>
@@ -423,34 +423,22 @@
     <t>Revisiting scattered light noise in 3G detectors: beam tube boundary effects  and optomechanical transfer functions</t>
   </si>
   <si>
-    <t>Straylight sources identification in optical benches through measurement at system-level</t>
-  </si>
-  <si>
     <t>marco</t>
   </si>
   <si>
     <t>Marc</t>
   </si>
   <si>
-    <t>Frederic</t>
-  </si>
-  <si>
     <t>nardello</t>
   </si>
   <si>
     <t>Andrés-Carcasona</t>
   </si>
   <si>
-    <t>Cleva</t>
-  </si>
-  <si>
     <t>CNRS, OCA Artemis</t>
   </si>
   <si>
     <t>MIT</t>
-  </si>
-  <si>
-    <t>CNRS</t>
   </si>
   <si>
     <t>Investigating the robustness of LIGO detectors to ground motion</t>
@@ -1197,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1205,7 +1193,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1268,16 +1256,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1285,16 +1273,16 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1305,16 +1293,16 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1361,16 +1349,16 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" t="s">
         <v>211</v>
       </c>
-      <c r="D2" t="s">
-        <v>215</v>
-      </c>
       <c r="E2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2" t="s">
         <v>218</v>
-      </c>
-      <c r="F2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1381,16 +1369,16 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" t="s">
         <v>219</v>
-      </c>
-      <c r="F3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1401,13 +1389,13 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" t="s">
         <v>216</v>
-      </c>
-      <c r="E4" t="s">
-        <v>220</v>
       </c>
       <c r="F4" t="s">
         <v>108</v>
@@ -1421,16 +1409,16 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" t="s">
         <v>217</v>
       </c>
-      <c r="E5" t="s">
-        <v>221</v>
-      </c>
       <c r="F5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1477,16 +1465,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1497,13 +1485,13 @@
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D3" t="s">
         <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F3" t="s">
         <v>72</v>
@@ -1546,10 +1534,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1560,10 +1548,10 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1574,10 +1562,10 @@
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1588,10 +1576,10 @@
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1602,10 +1590,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1616,10 +1604,10 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1630,10 +1618,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1644,10 +1632,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1658,10 +1646,10 @@
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -1687,7 +1675,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1695,7 +1683,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1703,7 +1691,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1711,7 +1699,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1719,7 +1707,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1727,7 +1715,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1735,7 +1723,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1743,7 +1731,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1751,7 +1739,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1759,7 +1747,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1767,7 +1755,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1775,7 +1763,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -1783,7 +1771,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -1791,7 +1779,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -1799,7 +1787,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -1807,7 +1795,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -1815,7 +1803,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -1823,7 +1811,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -1831,7 +1819,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -1839,7 +1827,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -1847,7 +1835,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -1855,7 +1843,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -1863,7 +1851,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -1871,7 +1859,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -1879,7 +1867,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -1887,7 +1875,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -1895,7 +1883,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -1903,7 +1891,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -2355,7 +2343,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2375,7 +2363,7 @@
         <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2561,7 +2549,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.6640625" customWidth="1"/>
@@ -2601,13 +2589,13 @@
         <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" t="s">
         <v>134</v>
-      </c>
-      <c r="F2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2621,30 +2609,13 @@
         <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" t="s">
         <v>135</v>
-      </c>
-      <c r="F3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2691,13 +2662,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F2" t="s">
         <v>67</v>
@@ -2711,16 +2682,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" t="s">
         <v>156</v>
-      </c>
-      <c r="F3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2731,16 +2702,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" t="s">
         <v>157</v>
-      </c>
-      <c r="F4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2751,16 +2722,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2771,16 +2742,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2791,16 +2762,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2811,16 +2782,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2831,16 +2802,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2851,16 +2822,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
       </c>
       <c r="E10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" t="s">
         <v>158</v>
-      </c>
-      <c r="F10" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -2871,16 +2842,16 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" t="s">
         <v>159</v>
-      </c>
-      <c r="F11" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2927,16 +2898,16 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
         <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2947,16 +2918,16 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2967,16 +2938,16 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2987,16 +2958,16 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -3007,16 +2978,16 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -3027,7 +2998,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
@@ -3047,16 +3018,16 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -3067,16 +3038,16 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F9" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -3087,16 +3058,16 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -3107,16 +3078,16 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
         <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -3127,16 +3098,16 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6232DE0A-300F-3E4E-8769-B448CD8B5303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6DB383-9F8A-AB46-A645-16AC3ED7DFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -2045,7 +2045,7 @@
         <v>83</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>157</v>
@@ -2085,7 +2085,7 @@
         <v>103</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
         <v>37</v>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E312E216-1DAA-804A-8C0E-35C36B0914EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC63196-946B-6443-99E9-46A63B1142F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="254">
   <si>
     <t>Key</t>
   </si>
@@ -1282,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.6640625" customWidth="1"/>
@@ -1389,6 +1389,26 @@
       </c>
       <c r="F5" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1432,7 +1452,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
         <v>206</v>
@@ -1452,7 +1472,7 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
         <v>207</v>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AB8A4D-4B9A-2F41-B510-5532285AD57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA4994B-3E00-5945-83E4-28BE2D4BB486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -2701,7 +2701,7 @@
         <v>93</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
         <v>132</v>
@@ -2801,7 +2801,7 @@
         <v>104</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
         <v>137</v>
@@ -2821,7 +2821,7 @@
         <v>206</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
         <v>256</v>
@@ -2977,7 +2977,7 @@
         <v>96</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>155</v>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA4994B-3E00-5945-83E4-28BE2D4BB486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18FBB5DB-DF13-3546-A966-7055BFE98B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -1232,7 +1232,7 @@
         <v>56</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>184</v>
@@ -1269,7 +1269,7 @@
         <v>80</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>186</v>
@@ -1325,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
         <v>196</v>
@@ -1345,7 +1345,7 @@
         <v>69</v>
       </c>
       <c r="B3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
         <v>197</v>
@@ -1365,7 +1365,7 @@
         <v>90</v>
       </c>
       <c r="B4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>198</v>
@@ -1385,7 +1385,7 @@
         <v>70</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
@@ -1405,7 +1405,7 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>73</v>
@@ -1460,9 +1460,6 @@
       <c r="A2">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>27</v>
-      </c>
       <c r="C2" t="s">
         <v>206</v>
       </c>
@@ -1481,7 +1478,7 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
         <v>207</v>
@@ -2997,7 +2994,7 @@
         <v>105</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>156</v>
@@ -3017,7 +3014,7 @@
         <v>108</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>157</v>
@@ -3037,7 +3034,7 @@
         <v>120</v>
       </c>
       <c r="B10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>158</v>
@@ -3057,7 +3054,7 @@
         <v>136</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>159</v>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBD2870-F1BE-D44B-83AA-187D841F8E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23CBC02-8555-E444-8705-4A7C2A1CBDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23CBC02-8555-E444-8705-4A7C2A1CBDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF8DD43-7E6F-0C47-8DE6-8C63E6E0765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -762,9 +762,6 @@
     <t>2025-05-15 18:00:00</t>
   </si>
   <si>
-    <t>2026-05-21 18:20:00</t>
-  </si>
-  <si>
     <t>National Astronomical Obsevatory of Japan</t>
   </si>
   <si>
@@ -802,6 +799,9 @@
   </si>
   <si>
     <t>Newtonian Noise Studies for LIGO and Cosmic Explorer</t>
+  </si>
+  <si>
+    <t>2026-05-23 18:20:00</t>
   </si>
 </sst>
 </file>
@@ -1533,7 +1533,7 @@
         <v>242</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1547,7 +1547,7 @@
         <v>242</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1561,7 +1561,7 @@
         <v>242</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1575,7 +1575,7 @@
         <v>242</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1586,10 +1586,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1600,10 +1600,10 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1614,10 +1614,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1628,10 +1628,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1642,10 +1642,10 @@
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2322,7 +2322,7 @@
         <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2342,7 +2342,7 @@
         <v>95</v>
       </c>
       <c r="F8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2373,16 +2373,16 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
+        <v>249</v>
+      </c>
+      <c r="D10" t="s">
         <v>250</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>251</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>252</v>
-      </c>
-      <c r="F10" t="s">
-        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -2707,10 +2707,10 @@
         <v>141</v>
       </c>
       <c r="E5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F5" t="s">
         <v>246</v>
-      </c>
-      <c r="F5" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2727,10 +2727,10 @@
         <v>141</v>
       </c>
       <c r="E6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" t="s">
         <v>246</v>
-      </c>
-      <c r="F6" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2747,10 +2747,10 @@
         <v>141</v>
       </c>
       <c r="E7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" t="s">
         <v>246</v>
-      </c>
-      <c r="F7" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2767,10 +2767,10 @@
         <v>141</v>
       </c>
       <c r="E8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F8" t="s">
         <v>246</v>
-      </c>
-      <c r="F8" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2787,10 +2787,10 @@
         <v>141</v>
       </c>
       <c r="E9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F9" t="s">
         <v>246</v>
-      </c>
-      <c r="F9" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2821,13 +2821,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" t="s">
         <v>254</v>
-      </c>
-      <c r="E11" t="s">
-        <v>255</v>
       </c>
       <c r="F11" t="s">
         <v>100</v>
@@ -2980,10 +2980,10 @@
         <v>141</v>
       </c>
       <c r="E7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" t="s">
         <v>246</v>
-      </c>
-      <c r="F7" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -3023,7 +3023,7 @@
         <v>173</v>
       </c>
       <c r="F9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">

--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/razzano/VirgoWork/gwadw2026/gwadw2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BF1C4B-7925-7A45-8E3D-63895EF37600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5E2B53-5B2C-504F-8C32-4E117FF6BF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24040" windowHeight="14060" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conference" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="245">
   <si>
     <t>Key</t>
   </si>
@@ -492,9 +492,6 @@
     <t>Advancing Gravitational-Wave Detection Through Ion Implantation for Low Coating Thermal Noise</t>
   </si>
   <si>
-    <t>Optimizing transmissive lens coatings over full apertures to mitigate loss</t>
-  </si>
-  <si>
     <t>Noise Sources in Crystalline Coatings for Gravitational-Wave Detectors</t>
   </si>
   <si>
@@ -522,9 +519,6 @@
     <t>Luca</t>
   </si>
   <si>
-    <t>Francisco</t>
-  </si>
-  <si>
     <t>Margot</t>
   </si>
   <si>
@@ -546,9 +540,6 @@
     <t>Massaro</t>
   </si>
   <si>
-    <t>Salces Carcoba</t>
-  </si>
-  <si>
     <t>Hennig</t>
   </si>
   <si>
@@ -573,9 +564,6 @@
     <t>Maastricht University &amp; Nikhef</t>
   </si>
   <si>
-    <t>UNM</t>
-  </si>
-  <si>
     <t>University of Glasgow</t>
   </si>
   <si>
@@ -588,36 +576,24 @@
     <t>Developing miniLISA: A Table-top Testbed for Validating Time-Delay Interferometry and Clock Noise Suppression for LISA</t>
   </si>
   <si>
-    <t>Residual force measurement during quasi-static release of a test mass for space applications</t>
-  </si>
-  <si>
     <t>Superconducting sensing and actuation for Einstein Telescope and Lunar Gravitational-wave Antenna</t>
   </si>
   <si>
     <t>Sourath</t>
   </si>
   <si>
-    <t>Tomotada</t>
-  </si>
-  <si>
     <t>Joris</t>
   </si>
   <si>
     <t>Ghosh</t>
   </si>
   <si>
-    <t>Akutsu</t>
-  </si>
-  <si>
     <t>van Heijningen</t>
   </si>
   <si>
     <t>Max Planck Institute for Gravitational Physics, Hanover, Germany</t>
   </si>
   <si>
-    <t>National Astronomical Observatory of Japan</t>
-  </si>
-  <si>
     <t>VU Amsterdam / Nikhef</t>
   </si>
   <si>
@@ -651,24 +627,12 @@
     <t>NAOJ</t>
   </si>
   <si>
-    <t>A Passive UV-Based System for Discharging the Test Masses of Ground Based Gravitational Wave Detectors</t>
-  </si>
-  <si>
     <t>Progress on an Electrostatic Violin Mode Damper for aLIGO</t>
   </si>
   <si>
-    <t>Saps</t>
-  </si>
-  <si>
-    <t>Buchman</t>
-  </si>
-  <si>
     <t>Rice</t>
   </si>
   <si>
-    <t>Stanford University</t>
-  </si>
-  <si>
     <t>pi5pm1</t>
   </si>
   <si>
@@ -801,7 +765,7 @@
     <t>Newtonian Noise Studies for LIGO and Cosmic Explorer</t>
   </si>
   <si>
-    <t>2026-05-23 18:20:00</t>
+    <t>2026-05-23 20:20:00</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1128,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1172,7 +1136,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1198,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.6640625" customWidth="1"/>
@@ -1235,53 +1199,36 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" t="s">
         <v>184</v>
       </c>
-      <c r="D2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" t="s">
-        <v>190</v>
-      </c>
       <c r="F2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>66</v>
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" t="s">
         <v>185</v>
       </c>
-      <c r="D3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E3" t="s">
-        <v>191</v>
-      </c>
       <c r="F3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>80</v>
-      </c>
-      <c r="B4">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -1328,16 +1275,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" t="s">
         <v>196</v>
-      </c>
-      <c r="D2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1348,16 +1295,16 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
         <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1368,13 +1315,13 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E4" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F4" t="s">
         <v>101</v>
@@ -1427,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.6640625" customWidth="1"/>
@@ -1458,38 +1405,21 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F3" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1530,10 +1460,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1544,10 +1474,10 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1558,10 +1488,10 @@
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1572,10 +1502,10 @@
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1586,10 +1516,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1600,10 +1530,10 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1614,10 +1544,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1628,10 +1558,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1642,10 +1572,10 @@
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -1671,7 +1601,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1679,7 +1609,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1687,7 +1617,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1695,7 +1625,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1703,7 +1633,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1711,7 +1641,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1719,7 +1649,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1727,7 +1657,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1735,7 +1665,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1743,7 +1673,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1751,7 +1681,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1759,7 +1689,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -1767,7 +1697,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -1775,7 +1705,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -1783,7 +1713,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -1791,7 +1721,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -1799,7 +1729,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -1807,7 +1737,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -1815,7 +1745,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -1823,7 +1753,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -1831,7 +1761,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -1839,7 +1769,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -1847,7 +1777,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -1855,7 +1785,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -1863,7 +1793,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -1871,7 +1801,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -1879,7 +1809,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -1887,7 +1817,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -2077,7 +2007,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -2322,7 +2252,7 @@
         <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2342,7 +2272,7 @@
         <v>95</v>
       </c>
       <c r="F8" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2373,16 +2303,16 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D10" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E10" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F10" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2707,10 +2637,10 @@
         <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F5" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2727,10 +2657,10 @@
         <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F6" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2747,10 +2677,10 @@
         <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F7" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2767,10 +2697,10 @@
         <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F8" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2787,10 +2717,10 @@
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F9" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2821,13 +2751,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F11" t="s">
         <v>100</v>
@@ -2840,7 +2770,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.6640625" customWidth="1"/>
@@ -2883,10 +2813,10 @@
         <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2900,13 +2830,13 @@
         <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2920,13 +2850,13 @@
         <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2940,130 +2870,113 @@
         <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>75</v>
+        <v>96</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="F6" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>169</v>
       </c>
       <c r="F7" t="s">
-        <v>246</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F8" t="s">
-        <v>181</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F9" t="s">
-        <v>247</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>136</v>
-      </c>
-      <c r="B11">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E11" t="s">
-        <v>175</v>
-      </c>
-      <c r="F11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
